--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GR 2 L</t>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MYK BTL 2 L</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,28 +31,28 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10010805</t>
-  </si>
-  <si>
-    <t>SANIA MYK GR PCH 2 L</t>
+    <t>20140913</t>
+  </si>
+  <si>
+    <t>SOVIA MYK GR 1.8 L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20140913</t>
-  </si>
-  <si>
-    <t>SOVIA MYK GR 1.8 L</t>
+    <t>10005838</t>
+  </si>
+  <si>
+    <t>FILMA MYK GR RF 2 L</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>MEIJI H/P STRW 42 G</t>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95 G</t>
   </si>
   <si>
     <t>4</t>
@@ -61,40 +61,34 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/P CHO 42 G</t>
+    <t>20084707</t>
+  </si>
+  <si>
+    <t>DK SUKRO OV BWG 95 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>MEIJI H/P D.CHO 42 G</t>
+    <t>20042632</t>
+  </si>
+  <si>
+    <t>IDM K ATOM PDS 140 G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHO 100 G</t>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM K JUMBO 80 G</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20069149</t>
-  </si>
-  <si>
-    <t>TANGO WFR VM 100 G</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -487,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -653,27 +647,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -31,28 +31,28 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20140913</t>
-  </si>
-  <si>
-    <t>SOVIA MYK GR 1.8 L</t>
+    <t>10010805</t>
+  </si>
+  <si>
+    <t>SANIA MYK GR PCH 2 L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10005838</t>
-  </si>
-  <si>
-    <t>FILMA MYK GR RF 2 L</t>
+    <t>10000442</t>
+  </si>
+  <si>
+    <t>FORTUNE MYK.GR R 2 L</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95 G</t>
+    <t>20069696</t>
+  </si>
+  <si>
+    <t>OISHI PPCR KRM 100 G</t>
   </si>
   <si>
     <t>4</t>
@@ -61,34 +61,34 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20084707</t>
-  </si>
-  <si>
-    <t>DK SUKRO OV BWG 95 G</t>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KCG ALMD 65 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20042632</t>
-  </si>
-  <si>
-    <t>IDM K ATOM PDS 140 G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20128291</t>
+  </si>
+  <si>
+    <t>IDM KCG ALMD MD 65 G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20096682</t>
-  </si>
-  <si>
-    <t>IDM K JUMBO 80 G</t>
+    <t>20022908</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY ALMD 82 G</t>
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -607,15 +607,15 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -624,18 +624,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -644,10 +644,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
